--- a/product_data.xlsx
+++ b/product_data.xlsx
@@ -522,7 +522,7 @@
       </c>
       <c r="B2" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-Enterprise-10G</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -539,7 +539,7 @@
       </c>
       <c r="B3" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-Enterprise-20G</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -556,7 +556,7 @@
       </c>
       <c r="B4" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH2150B</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -573,7 +573,7 @@
       </c>
       <c r="B5" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH2300B</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -590,7 +590,7 @@
       </c>
       <c r="B6" s="6" t="inlineStr">
         <is>
-          <t>AF-1000-SK1305B</t>
+          <t>FW-SK1305B</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -607,7 +607,7 @@
       </c>
       <c r="B7" s="6" t="inlineStr">
         <is>
-          <t>AF-1000-SK1308A</t>
+          <t>FW-SK1308A</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -624,7 +624,7 @@
       </c>
       <c r="B8" s="6" t="inlineStr">
         <is>
-          <t>AF-1000-SK1505A</t>
+          <t>FW-SK1505A</t>
         </is>
       </c>
       <c r="C8" s="4" t="inlineStr">
@@ -641,7 +641,7 @@
       </c>
       <c r="B9" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH1300A</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
@@ -658,7 +658,7 @@
       </c>
       <c r="B10" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH1200B</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
@@ -675,7 +675,7 @@
       </c>
       <c r="B11" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-Mid-Range-2G</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
@@ -692,7 +692,7 @@
       </c>
       <c r="B12" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-Mid-Range-4G</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
@@ -709,7 +709,7 @@
       </c>
       <c r="B13" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH1800A</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
@@ -726,7 +726,7 @@
       </c>
       <c r="B14" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH2100B</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
@@ -743,7 +743,7 @@
       </c>
       <c r="B15" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH2130B</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
@@ -760,7 +760,7 @@
       </c>
       <c r="B16" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH2150A</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
@@ -777,7 +777,7 @@
       </c>
       <c r="B17" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH2250B</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
@@ -794,7 +794,7 @@
       </c>
       <c r="B18" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH2350B</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
@@ -811,7 +811,7 @@
       </c>
       <c r="B19" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH2350A</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
@@ -828,7 +828,7 @@
       </c>
       <c r="B20" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH2600A</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="B21" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH3120B</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
@@ -862,12 +862,13 @@
       </c>
       <c r="B22" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH3220A</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>网络层吞吐量:100G;应用层吞吐量:40G;防病毒吞吐量:19G;IPS吞吐量:24G;全威胁吞吐量:16G;并发连接数:2000万;HTTP新建连接数:80万;SSL VPN推荐用户数（单独购买）:55;SSL VPN最大用户数（单独购买）:260;SSL VPN最大理论加密流量（单独购买）:650M;IPSec VPN 最大接入数:25000;IPSec VPN吞吐量:8G;规格:2U; 电源:冗余电源; 接口：4千兆电口; 4千兆光口SFP; 8万兆光口SFP+;</t>
+          <t xml:space="preserve">	
+网络层吞吐量:100G;应用层吞吐量:40G;防病毒吞吐量:19G;IPS吞吐量:24G;全威胁吞吐量:16G;并发连接数:2000万;HTTP新建连接数:80万;SSL VPN推荐用户数（单独购买）:55;SSL VPN最大用户数（单独购买）:260;SSL VPN最大理论加密流量（单独购买）:650M;IPSec VPN 最大接入数:25000;IPSec VPN吞吐量:8G;规格:2U; 电源:冗余电源; 接口：4千兆电口; 4千兆光口SFP; 8万兆光口SFP+;</t>
         </is>
       </c>
     </row>
@@ -879,7 +880,7 @@
       </c>
       <c r="B23" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH3400A</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
@@ -896,7 +897,7 @@
       </c>
       <c r="B24" s="6" t="inlineStr">
         <is>
-          <t>FW-Mid-Range</t>
+          <t>FW-FH3500A</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
@@ -913,7 +914,7 @@
       </c>
       <c r="B25" s="3" t="inlineStr">
         <is>
-          <t>AF-1000-B1080</t>
+          <t>FW-B1080</t>
         </is>
       </c>
       <c r="C25" s="1" t="inlineStr">
@@ -930,7 +931,7 @@
       </c>
       <c r="B26" s="2" t="inlineStr">
         <is>
-          <t>AF-1000-B1120</t>
+          <t>FW-B1120</t>
         </is>
       </c>
       <c r="C26" s="1" t="inlineStr">
@@ -995,7 +996,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-Mid-Range-60M</t>
         </is>
       </c>
       <c r="C2" s="4" t="inlineStr">
@@ -1012,7 +1013,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-Mid-Range-100M</t>
         </is>
       </c>
       <c r="C3" s="4" t="inlineStr">
@@ -1029,7 +1030,7 @@
       </c>
       <c r="B4" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-Mid-Range-200M</t>
         </is>
       </c>
       <c r="C4" s="4" t="inlineStr">
@@ -1046,7 +1047,7 @@
       </c>
       <c r="B5" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-Enterprise-300M</t>
         </is>
       </c>
       <c r="C5" s="4" t="inlineStr">
@@ -1063,7 +1064,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-Enterprise-500M</t>
         </is>
       </c>
       <c r="C6" s="4" t="inlineStr">
@@ -1080,7 +1081,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-B1750</t>
         </is>
       </c>
       <c r="C7" s="4" t="inlineStr">
@@ -1097,7 +1098,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-Enterprise-1G</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
@@ -1114,7 +1115,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-Enterprise-2G</t>
         </is>
       </c>
       <c r="C9" s="4" t="inlineStr">
@@ -1131,7 +1132,8 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t xml:space="preserve">IB-B2250
+</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
@@ -1148,7 +1150,7 @@
       </c>
       <c r="B11" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-B2500</t>
         </is>
       </c>
       <c r="C11" s="4" t="inlineStr">
@@ -1165,12 +1167,13 @@
       </c>
       <c r="B12" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-B3100</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>网络层吞吐量（大包）:30G;应用层吞吐量:15Gb;带宽性能:10Gb;支持用户数:100000;准入终端数（支持客户端授权-需单独收费）:3000;准入终端数的扩容上限（支持客户端授权-需单独收费）:20000;防泄密终端数上限(需单独收费):35000;包转发率:1.8Mpps;每秒新建连接数:200000;最大并发连接数:8000000;规格:2U; 电源:冗余电源; 接口：4千兆电口; 4千兆光口SFP; 4万兆光口SFP+;</t>
+          <t xml:space="preserve">	
+网络层吞吐量（大包）:30G;应用层吞吐量:15Gb;带宽性能:10Gb;支持用户数:100000;准入终端数（支持客户端授权-需单独收费）:3000;准入终端数的扩容上限（支持客户端授权-需单独收费）:20000;防泄密终端数上限(需单独收费):35000;包转发率:1.8Mpps;每秒新建连接数:200000;最大并发连接数:8000000;规格:2U; 电源:冗余电源; 接口：4千兆电口; 4千兆光口SFP; 4万兆光口SFP+;</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1185,13 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-B3200</t>
         </is>
       </c>
       <c r="C13" s="4" t="inlineStr">
         <is>
-          <t>网络层吞吐量（大包）:40G;应用层吞吐量:30Gb;带宽性能:20Gb;支持用户数:200000;准入终端数（支持客户端授权-需单独收费）:3000;准入终端数的扩容上限（支持客户端授权-需单独收费）:20000;防泄密终端数上限(需单独收费):40000;包转发率:3.6Mpps;每秒新建连接数:250000;最大并发连接数:14000000;规格:2U; 电源:冗余电源; 接口：4千兆电口; 4千兆光口SFP; 4万兆光口SFP+;</t>
+          <t xml:space="preserve">	
+网络层吞吐量（大包）:40G;应用层吞吐量:30Gb;带宽性能:20Gb;支持用户数:200000;准入终端数（支持客户端授权-需单独收费）:3000;准入终端数的扩容上限（支持客户端授权-需单独收费）:20000;防泄密终端数上限(需单独收费):40000;包转发率:3.6Mpps;每秒新建连接数:250000;最大并发连接数:14000000;规格:2U; 电源:冗余电源; 接口：4千兆电口; 4千兆光口SFP; 4万兆光口SFP+;</t>
         </is>
       </c>
     </row>
@@ -1199,7 +1203,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-B3300</t>
         </is>
       </c>
       <c r="C14" s="4" t="inlineStr">
@@ -1216,7 +1220,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-B3400</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1233,7 +1237,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>AC-1000-SK1200</t>
+          <t>IB-SK1200</t>
         </is>
       </c>
       <c r="C16" s="4" t="inlineStr">
@@ -1250,7 +1254,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>AC-1000-SK1300</t>
+          <t>IB-SK1300</t>
         </is>
       </c>
       <c r="C17" s="4" t="inlineStr">
@@ -1267,7 +1271,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>AC-1000-SK1500</t>
+          <t>IB-SK1500</t>
         </is>
       </c>
       <c r="C18" s="4" t="inlineStr">
@@ -1284,7 +1288,7 @@
       </c>
       <c r="B19" s="4" t="inlineStr">
         <is>
-          <t>AC-1000-SK2100</t>
+          <t>IB-SK2100</t>
         </is>
       </c>
       <c r="C19" s="4" t="inlineStr">
@@ -1301,7 +1305,7 @@
       </c>
       <c r="B20" s="4" t="inlineStr">
         <is>
-          <t>AC-1000-SK2200</t>
+          <t>IB-SK2200</t>
         </is>
       </c>
       <c r="C20" s="4" t="inlineStr">
@@ -1318,7 +1322,7 @@
       </c>
       <c r="B21" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-Mid-Range-60M</t>
         </is>
       </c>
       <c r="C21" s="4" t="inlineStr">
@@ -1335,7 +1339,7 @@
       </c>
       <c r="B22" s="4" t="inlineStr">
         <is>
-          <t>NAC-Mid-Range</t>
+          <t>IB-Mid-Range-100M</t>
         </is>
       </c>
       <c r="C22" s="4" t="inlineStr">
@@ -1433,7 +1437,7 @@
       </c>
       <c r="B2" s="2" t="inlineStr">
         <is>
-          <t>LogAudit-Std</t>
+          <t>LOG-Basic-20</t>
         </is>
       </c>
       <c r="C2" s="3" t="inlineStr">
@@ -1450,7 +1454,7 @@
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>LogAudit-Std</t>
+          <t>LOG-Standard-50</t>
         </is>
       </c>
       <c r="C3" s="3" t="inlineStr">
@@ -1467,7 +1471,7 @@
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>LogAudit-Std</t>
+          <t>LOG-Enterprise-100</t>
         </is>
       </c>
       <c r="C4" s="3" t="inlineStr">
@@ -1484,7 +1488,7 @@
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>LogAudit-Std</t>
+          <t>LOG-Basic-200</t>
         </is>
       </c>
       <c r="C5" s="3" t="inlineStr">
@@ -1501,7 +1505,7 @@
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>LogAudit-Std</t>
+          <t>LOG-V300</t>
         </is>
       </c>
       <c r="C6" s="3" t="inlineStr">
@@ -1518,7 +1522,7 @@
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>LogAudit-Std</t>
+          <t>LOG-Standard-500</t>
         </is>
       </c>
       <c r="C7" s="3" t="inlineStr">
@@ -1535,7 +1539,7 @@
       </c>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>SIP-Logger-A600标准产品</t>
+          <t>LOG-A600标准产品</t>
         </is>
       </c>
       <c r="C8" s="3" t="inlineStr">
@@ -1552,7 +1556,7 @@
       </c>
       <c r="B9" s="2" t="inlineStr">
         <is>
-          <t>SIP-Logger-C600标准产品</t>
+          <t>LOG-C600标准产品</t>
         </is>
       </c>
       <c r="C9" s="3" t="inlineStr">
@@ -1569,12 +1573,12 @@
       </c>
       <c r="B10" s="2" t="inlineStr">
         <is>
-          <t>SIP-Logger-E600标准产品</t>
+          <t>LOG-E600标准产品</t>
         </is>
       </c>
       <c r="C10" s="3" t="inlineStr">
         <is>
-          <t>默认包含主机审计许可证书数量:500;最大可扩展审计主机许可数:1500;可用存储量:8TB（RAID1 模式）;平均每秒处理日志数（eps）最大性能:6000;规格:2U; 电源:冗余电源; 接口：6千兆电口; 2万兆光口SFP+;</t>
+          <t xml:space="preserve">	默认包含主机审计许可证书数量:500;最大可扩展审计主机许可数:1500;可用存储量:8TB（RAID1 模式）;平均每秒处理日志数（eps）最大性能:6000;规格:2U; 电源:冗余电源; 接口：6千兆电口; 2万兆光口SFP+;</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1661,7 @@
     <row r="2" ht="80" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>ZTNA-Gateway</t>
+          <t>ZT-Basic-300</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1669,7 +1673,7 @@
     <row r="3" ht="80" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>ZTNA-Gateway</t>
+          <t>ZT-Standard-500</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1681,12 +1685,13 @@
     <row r="4" ht="83.7" customFormat="1" customHeight="1" s="2">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>ZTNA-Gateway</t>
+          <t>ZT-1000-B1080M</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>最大理论加密流量（Mbps）:600;最大理论建议并发用户数:1200;最大理论https并发连接数（个）:60000;理论https新建连接数（个/秒）:240;加密最大流量（Mbps）:170;理论并发隧道数（Tunnel）:600;规格:1U; 电源:冗余电源; 接口：6千兆电口; 4千兆光口SFP;</t>
+          <t xml:space="preserve">	
+最大理论加密流量（Mbps）:600;最大理论建议并发用户数:1200;最大理论https并发连接数（个）:60000;理论https新建连接数（个/秒）:240;加密最大流量（Mbps）:170;理论并发隧道数（Tunnel）:600;规格:1U; 电源:冗余电源; 接口：6千兆电口; 4千兆光口SFP;</t>
         </is>
       </c>
     </row>
@@ -1748,7 +1753,7 @@
     <row r="2" ht="80" customFormat="1" customHeight="1" s="2">
       <c r="A2" s="6" t="inlineStr">
         <is>
-          <t>PAM-Appliance</t>
+          <t>BA-Mid-Range-50</t>
         </is>
       </c>
       <c r="B2" s="4" t="inlineStr">
@@ -1761,17 +1766,18 @@
     <row r="3" ht="249" customFormat="1" customHeight="1" s="2">
       <c r="A3" s="6" t="inlineStr">
         <is>
-          <t>PAM-Appliance</t>
+          <t>BA-Enterprise-200</t>
         </is>
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>默认包含运维授权数:200;最大可扩展资产数:1000;图形运维最大并发数:200;字符运维最大并发数:350;规格:2U; 电源:单电源; 接口：6千兆电口; 2万兆光口SFP+;</t>
+          <t xml:space="preserve">	
+默认包含运维授权数:200;最大可扩展资产数:1000;图形运维最大并发数:200;字符运维最大并发数:350;规格:2U; 电源:单电源; 接口：6千兆电口; 2万兆光口SFP+;</t>
         </is>
       </c>
       <c r="C3" s="17" t="inlineStr">
         <is>
-          <t>产品型号	PAM-Appliance
+          <t>产品型号	BA-Enterprise-200
 硬件配置	内存大小	8GB
 硬盘容量	128GB SSD+2TB SATA
 技术规范：(长 x 宽 x 高(mm)600mm(L)*440mm(W)*89mm(H)
@@ -1842,7 +1848,7 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="9" t="inlineStr">
         <is>
-          <t>aSerer-W-2105P</t>
+          <t>HCI-2U-Basic</t>
         </is>
       </c>
       <c r="B2" s="3" t="inlineStr">
@@ -1854,7 +1860,7 @@
     <row r="3" ht="80" customHeight="1">
       <c r="A3" s="9" t="inlineStr">
         <is>
-          <t>HCI-Node</t>
+          <t>HCI-2U-Standard</t>
         </is>
       </c>
       <c r="B3" s="3" t="inlineStr">
@@ -1866,7 +1872,7 @@
     <row r="4" ht="80" customHeight="1">
       <c r="A4" s="9" t="inlineStr">
         <is>
-          <t>HCI-Node</t>
+          <t>HCI-W-2205</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -1878,7 +1884,7 @@
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="9" t="inlineStr">
         <is>
-          <t>HCI-Node</t>
+          <t>HCI-W-4000</t>
         </is>
       </c>
       <c r="B5" s="3" t="inlineStr">
@@ -1890,7 +1896,7 @@
     <row r="6" ht="80" customHeight="1">
       <c r="A6" s="9" t="inlineStr">
         <is>
-          <t>aServer-W-G2400</t>
+          <t>HCI-W-G2400</t>
         </is>
       </c>
       <c r="B6" s="3" t="inlineStr">
@@ -1902,7 +1908,7 @@
     <row r="7" ht="80" customHeight="1">
       <c r="A7" s="9" t="inlineStr">
         <is>
-          <t>HCI-Node</t>
+          <t>HCI-2U-StandardP</t>
         </is>
       </c>
       <c r="B7" s="3" t="inlineStr">
@@ -1914,7 +1920,7 @@
     <row r="8" ht="80" customHeight="1">
       <c r="A8" s="9" t="inlineStr">
         <is>
-          <t>HCI-Node</t>
+          <t>HCI-W-2205F</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -1926,7 +1932,7 @@
     <row r="9" ht="80" customHeight="1">
       <c r="A9" s="9" t="inlineStr">
         <is>
-          <t>aserver-W-2405</t>
+          <t>HCI-W-2405</t>
         </is>
       </c>
       <c r="B9" s="3" t="inlineStr">
@@ -1938,7 +1944,7 @@
     <row r="10" ht="80" customHeight="1">
       <c r="A10" s="9" t="inlineStr">
         <is>
-          <t>aServer-R-2205</t>
+          <t>HCI-R-2205</t>
         </is>
       </c>
       <c r="B10" s="3" t="inlineStr">
@@ -1950,19 +1956,20 @@
     <row r="11" ht="80" customHeight="1">
       <c r="A11" s="9" t="inlineStr">
         <is>
-          <t>HCI-Node</t>
+          <t>HCI-W-4000F</t>
         </is>
       </c>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>CPU型号:Intel Xeon Gold 5318H 2.50 GHz; CPU个数:4; 每个CPU核数:18; 每个CPU线程数:36; 内存:4 * 32GB; 系统盘:2 * 480GB; 缓存盘:选配; 数据盘:选配; 标配盘位数:16; 电源:冗余电源; 接口：2千兆电口; 4万兆光口;</t>
+          <t xml:space="preserve">	
+CPU型号:Intel Xeon Gold 5318H 2.50 GHz; CPU个数:4; 每个CPU核数:18; 每个CPU线程数:36; 内存:4 * 32GB; 系统盘:2 * 480GB; 缓存盘:选配; 数据盘:选配; 标配盘位数:16; 电源:冗余电源; 接口：2千兆电口; 4万兆光口;</t>
         </is>
       </c>
     </row>
     <row r="12" ht="80" customHeight="1">
       <c r="A12" s="9" t="inlineStr">
         <is>
-          <t>aServer-E-2705</t>
+          <t>HCI-E-2705</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1974,7 +1981,7 @@
     <row r="13" ht="80" customHeight="1">
       <c r="A13" s="9" t="inlineStr">
         <is>
-          <t>aServer-E-1905</t>
+          <t>HCI-E-1905</t>
         </is>
       </c>
       <c r="B13" s="3" t="inlineStr">
@@ -1986,7 +1993,7 @@
     <row r="14" ht="80" customHeight="1">
       <c r="A14" s="9" t="inlineStr">
         <is>
-          <t>aServer-E-2805</t>
+          <t>HCI-E-2805</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -2058,19 +2065,20 @@
     <row r="2" ht="80" customHeight="1">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>VDS-B-G690</t>
+          <t>VDI-2U-Basic</t>
         </is>
       </c>
       <c r="B2" s="10" t="inlineStr">
         <is>
-          <t>CPU型号:AMD Milan 73F3 3.5GHZ; CPU个数:2; 每个CPU核数:16; 每个CPU线程数:32; 内存:8 * 32GB; 系统盘:1 * 480GB; 缓存盘:选配; 数据盘:选配; 标配盘位数:8; 电源:冗余电源; 接口：4千兆电口; 2万兆光口;</t>
+          <t xml:space="preserve">	
+CPU型号:AMD Milan 73F3 3.5GHZ; CPU个数:2; 每个CPU核数:16; 每个CPU线程数:32; 内存:8 * 32GB; 系统盘:1 * 480GB; 缓存盘:选配; 数据盘:选配; 标配盘位数:8; 电源:冗余电源; 接口：4千兆电口; 2万兆光口;</t>
         </is>
       </c>
     </row>
     <row r="3" ht="80" customHeight="1">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>VDI-Host</t>
+          <t>VDI-2U-Standard</t>
         </is>
       </c>
       <c r="B3" s="10" t="inlineStr">
@@ -2082,7 +2090,7 @@
     <row r="4" ht="80" customHeight="1">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>VDI-Host</t>
+          <t>VDI-7850</t>
         </is>
       </c>
       <c r="B4" s="10" t="inlineStr">
@@ -2094,7 +2102,7 @@
     <row r="5" ht="80" customHeight="1">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>VDI-Host</t>
+          <t>VDI-7800</t>
         </is>
       </c>
       <c r="B5" s="10" t="inlineStr">
@@ -2123,7 +2131,8 @@
       </c>
       <c r="B7" s="10" t="inlineStr">
         <is>
-          <t>CPU型号:Intel 6334 3.6GHz; CPU个数:2; 每个CPU核数:8; 每个CPU线程数:16; 内存:4 * 32GB; 系统盘:1 * 240GB; 缓存盘:选配; 数据盘:选配; 标配盘位数:8; 电源:冗余电源; 接口：4千兆电口; 2万兆光口;</t>
+          <t xml:space="preserve">	
+CPU型号:Intel 6334 3.6GHz; CPU个数:2; 每个CPU核数:8; 每个CPU线程数:16; 内存:4 * 32GB; 系统盘:1 * 240GB; 缓存盘:选配; 数据盘:选配; 标配盘位数:8; 电源:冗余电源; 接口：4千兆电口; 2万兆光口;</t>
         </is>
       </c>
     </row>
@@ -2135,7 +2144,8 @@
       </c>
       <c r="B8" s="10" t="inlineStr">
         <is>
-          <t>CPU型号:intel(R) Xeon(R) Silver 4314 CPU@2.40GHZ; CPU个数:2; 每个CPU核数:16; 每个CPU线程数:32; 内存:8 * 32GB; 系统盘:2 * 240GB; 缓存盘:选配; 数据盘:选配; 标配盘位数:12; 电源:冗余电源; 接口：4千兆电口; 2万兆光口;</t>
+          <t xml:space="preserve">	
+CPU型号:intel(R) Xeon(R) Silver 4314 CPU@2.40GHZ; CPU个数:2; 每个CPU核数:16; 每个CPU线程数:32; 内存:8 * 32GB; 系统盘:2 * 240GB; 缓存盘:选配; 数据盘:选配; 标配盘位数:12; 电源:冗余电源; 接口：4千兆电口; 2万兆光口;</t>
         </is>
       </c>
     </row>
@@ -2159,7 +2169,8 @@
       </c>
       <c r="B10" s="10" t="inlineStr">
         <is>
-          <t>CPU型号:intel(R) Xeon(R) Gold 6342 CPU@2.80GHZ; CPU个数:2; 每个CPU核数:24; 每个CPU线程数:48; 内存:8 * 32GB; 系统盘:2 * 240GB; 缓存盘:选配; 数据盘:选配; 标配盘位数:12; 电源:冗余电源; 接口：4千兆电口; 2万兆光口;</t>
+          <t xml:space="preserve">	
+CPU型号:intel(R) Xeon(R) Gold 6342 CPU@2.80GHZ; CPU个数:2; 每个CPU核数:24; 每个CPU线程数:48; 内存:8 * 32GB; 系统盘:2 * 240GB; 缓存盘:选配; 数据盘:选配; 标配盘位数:12; 电源:冗余电源; 接口：4千兆电口; 2万兆光口;</t>
         </is>
       </c>
     </row>
